--- a/Tableau_Data_ESG_Poland.xlsx
+++ b/Tableau_Data_ESG_Poland.xlsx
@@ -1766,31 +1766,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Issue_Type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Impact_on_Comparability</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>Resolution</t>
         </is>
@@ -1809,17 +1809,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Scope 2 market-based (207,858 t) higher than location-based (135,019 t): no guarantees of origin, residual mix factor 808.3 vs grid average 524.9 tCO2/GWh</t>
+          <t>Scope 3 is 96.6% of total; category 1 (purchased goods) is spend-based using Climatiq factors. Company states high measurement uncertainty</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MB total higher than LB; not an error</t>
+          <t>Intensity driven by an estimate</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kept both values; totals use MB</t>
+          <t>Flagged in README</t>
         </is>
       </c>
     </row>
@@ -1836,17 +1836,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scope 3 is 96.6% of total; category 1 (purchased goods) is spend-based using Climatiq factors. Company states high measurement uncertainty</t>
+          <t>Location-based factor uses KOBIZE 2024 value for 2025 consumption (latest available)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Intensity driven by an estimate</t>
+          <t>One-year lag in grid factor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Flagged in README</t>
+          <t>Noted, no adjustment</t>
         </is>
       </c>
     </row>
@@ -1858,29 +1858,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Methodology unclear</t>
+          <t>Boundary or scope difference</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Location-based factor uses KOBIZE 2024 value for 2025 consumption (latest available)</t>
+          <t>Taxonomy turnover KPI not assessed: eligible activities below 10% materiality threshold (Delegated Reg. 2026/73)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>One-year lag in grid factor</t>
+          <t>0% not comparable with companies that assessed the KPI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Noted, no adjustment</t>
+          <t>Recorded as 0%, flagged</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dino Polska</t>
+          <t>Allegro.eu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1890,44 +1890,44 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taxonomy turnover KPI not assessed: eligible activities below 10% materiality threshold (Delegated Reg. 2026/73)</t>
+          <t>Emissions include Mall South (Slovenia, Croatia; held for sale at 31.12.2025, SPA signed 7 Jan 2026). Its revenue (PLN 427.7m) sits in discontinued operations (note 18.2) and was added back to match the emissions boundary</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0% not comparable with companies that assessed the KPI</t>
+          <t>Continuing revenue only would overstate intensity by 5.8%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recorded as 0%, flagged</t>
+          <t>Revenue = 11,458.1 + 427.7 = 11,885.8 PLN m</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dino Polska</t>
+          <t>Allegro.eu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Methodology unclear</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No GHG reduction targets disclosed (E1-6 target columns empty, no formal transition plan in E1-1)</t>
+          <t>Reported intensity (35.1) is reproduced only with revenue plus other operating income incl. discontinued (PLN 12,103.4m). Net revenue only gives 35.8 (+2.0%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cannot assess progress against targets</t>
+          <t>Reported intensity slightly understated vs strict net revenue</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Noted in README</t>
+          <t>Kept net revenue for consistency across companies</t>
         </is>
       </c>
     </row>
@@ -1939,22 +1939,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Boundary or scope difference</t>
+          <t>Restatement</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Emissions include Mall South (Slovenia, Croatia; held for sale at 31.12.2025, SPA signed 7 Jan 2026). Its revenue (PLN 427.7m) sits in discontinued operations (note 18.2) and was added back to match the emissions boundary</t>
+          <t>2024 Scope 3 restated using primary supplier data; Polish Operations category 1 cut from 235,321 to 146,733 tCO2e</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Continuing revenue only would overstate intensity by 5.8%</t>
+          <t>2024 comparatives in older reports not comparable</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Revenue = 11,458.1 + 427.7 = 11,885.8 PLN m</t>
+          <t>Only 2025 used</t>
         </is>
       </c>
     </row>
@@ -1966,22 +1966,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Methodology unclear</t>
+          <t>Boundary or scope difference</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reported intensity (35.1) uses revenue plus other operating income incl. discontinued (PLN 12,103.4m). Net revenue only gives 35.8 (+2.0%)</t>
+          <t>Report shows Group and Polish Operations separately; Group used. Non-Polish operations ~22% of market-based total</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Reported intensity slightly understated vs strict net revenue</t>
+          <t>Mixing boundaries would distort comparison</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kept net revenue for consistency across companies</t>
+          <t>Group boundary for all companies</t>
         </is>
       </c>
     </row>
@@ -1993,76 +1993,76 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Restatement</t>
+          <t>Methodology unclear</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024 Scope 3 restated using primary supplier data; Polish Operations category 1 cut from 235,321 to 146,733 tCO2e</t>
+          <t>SBTi target -43% Scope 1+2 by 2030 described as vs 2024 in strategy text but vs 2021 base year elsewhere (14.2 kt matches 2021). 2025 MB Scope 1+2 (5.8 kt) already below 2030 level, driven by guarantees of origin (58% renewable); location-based Scope 1+2 is +35% vs 2021</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024 comparatives in older reports not comparable</t>
+          <t>Market-based progress relies on certificates, not lower consumption</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Only 2025 used</t>
+          <t>Flagged in README</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Allegro.eu</t>
+          <t>Orange Polska</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Boundary or scope difference</t>
+          <t>Unit inconsistency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Report shows Group and Polish Operations separately; Group used. Non-Polish operations ~22% of market-based total</t>
+          <t>Intensity reported per PLN thousand and rounded to 2 decimals (0.04), i.e. 35-45 t per PLN m (+/-12%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mixing boundaries would distort comparison</t>
+          <t>Validation much less precise than for other companies</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Group boundary for all companies</t>
+          <t>Converted to t/PLN m; computed 39.75</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Allegro.eu</t>
+          <t>Orange Polska</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Methodology unclear</t>
+          <t>Boundary or scope difference</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SBTi target -43% Scope 1+2 by 2030 described as vs 2024 in strategy text but vs 2021 base year elsewhere (14.2 kt matches 2021). 2025 MB Scope 1+2 (5.8 kt) already below 2030 level, driven by guarantees of origin (58% renewable); location-based Scope 1+2 is +35% vs 2021</t>
+          <t>Orange Energia (electricity resale) sold in H1 2025; Scope 3 includes its H1 emissions (22,296 t, cat. 3.3). Totals excluding OE also disclosed (Scope 3: 455,963 t)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Market-based progress relies on certificates, not lower consumption</t>
+          <t>Scope 3 falls partly due to divestment, not reductions</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Flagged in README</t>
+          <t>Used totals incl. OE, consistent with reported intensity</t>
         </is>
       </c>
     </row>
@@ -2074,22 +2074,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unit inconsistency</t>
+          <t>Boundary or scope difference</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Intensity reported per PLN thousand and rounded to 2 decimals (0.04), i.e. 35-45 t per PLN m (+/-12%)</t>
+          <t>Emissions consolidated under operational control, while Dino and Allegro follow the financial consolidation boundary</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Validation much less precise than for other companies</t>
+          <t>Small boundary differences across companies</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Converted to t/PLN m; computed 39.75</t>
+          <t>Noted, no adjustment</t>
         </is>
       </c>
     </row>
@@ -2106,24 +2106,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orange Energia (electricity resale) sold in H1 2025; Scope 3 includes its H1 emissions (22,296 t, cat. 3.3). Totals excluding OE also disclosed (Scope 3: 455,963 t)</t>
+          <t>Taxonomy alignment not assessed in 2025: &gt;90% of activity not eligible, materiality exemption (Reg. 2026/73)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Scope 3 falls partly due to divestment, not reductions</t>
+          <t>0% means not assessed, not confirmed non-aligned</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Used totals incl. OE, consistent with reported intensity</t>
+          <t>Recorded as 0%, flagged</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Orange Polska</t>
+          <t>Grupa Zabka</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2133,24 +2133,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Emissions consolidated under operational control, while Dino and Allegro follow the financial consolidation boundary</t>
+          <t>Franchise model: emissions of franchised stores (242,231 t) are in Scope 3 category 14, while Dino reports store energy in Scope 1 and 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Small boundary differences across companies</t>
+          <t>Scope 1+2 not comparable with Dino; only total (Scope 1+2+3) intensity is comparable</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Noted, no adjustment</t>
+          <t>Compare food retailers on total (S1+2+3) intensity only</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Orange Polska</t>
+          <t>Grupa Zabka</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2160,24 +2160,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scope 2 market-based 97% below location-based (7,354 vs 272,838 t): 100% renewable electricity via PPAs and guarantees of origin without PPA (114,028 MWh)</t>
+          <t>Location-based total (3,592,616 t) exceeds Scope 1 + Scope 2 LB + reported Scope 3 by 155,536 t; likely Scope 3 (e.g. franchise electricity) recalculated location-based, not disclosed separately</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Market-based progress relies on contractual instruments</t>
+          <t>LB totals cannot be rebuilt from disclosed components</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kept both values</t>
+          <t>Market-based totals used (they reconcile exactly)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Orange Polska</t>
+          <t>Grupa Zabka</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2187,17 +2187,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Taxonomy alignment not assessed in 2025: &gt;90% of activity not eligible, materiality exemption (Reg. 2026/73)</t>
+          <t>Report gives Group and Zabka Polska (about 90% of emissions) figures separately; Group intensity disclosed for the first time (no 2024 comparative)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0% means not assessed, not confirmed non-aligned</t>
+          <t>Mixing boundaries would distort comparison</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recorded as 0%, flagged</t>
+          <t>Group figures used</t>
         </is>
       </c>
     </row>
@@ -2214,51 +2214,51 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Franchise model: emissions of franchised stores (242,231 t) are in Scope 3 category 14, while Dino reports store energy in Scope 1 and 2</t>
+          <t>Taxonomy: no eligible or aligned turnover; CapEx aligned 8.2% (eligible 58.2%, logistics centres); OpEx not material under exemption</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Scope 1+2 and per-employee KPIs not comparable between Dino and Zabka; use total intensity</t>
+          <t>OpEx 0% means not assessed</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Compare food retailers on total (S1+2+3) intensity only</t>
+          <t>Recorded as 0%, flagged</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Grupa Zabka</t>
+          <t>Grupa Kety</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Missing value</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Only 4,257 employees (headcount): franchisee staff are not Group employees (Dino: 55,856)</t>
+          <t>Only location-based GHG intensity disclosed (242.7 t/PLN m); market-based intensity missing although ESRS E1-6 requires both</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Emissions per employee meaningless across business models</t>
+          <t>Automatic MB check not possible</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Excluded from cross-company comparison</t>
+          <t>Recomputed LB: 1,333,852 / 5,494.6 = 242.8, matches. Computed MB: 244.0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Grupa Zabka</t>
+          <t>Grupa Kety</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2268,51 +2268,51 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Location-based total (3,592,616 t) exceeds Scope 1 + Scope 2 LB + reported Scope 3 by 155,536 t; likely Scope 3 (e.g. franchise electricity) recalculated location-based, not disclosed separately</t>
+          <t>Scope 2 market-based (118,957 t) above location-based (112,196 t) despite 20,030 MWh of guarantees of origin; MB uses supplier-specific factors</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LB totals cannot be rebuilt from disclosed components</t>
+          <t>Same pattern as Dino</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Market-based totals used (they reconcile exactly)</t>
+          <t>Kept both values</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Grupa Zabka</t>
+          <t>Grupa Kety</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Boundary or scope difference</t>
+          <t>Methodology unclear</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Report gives Group and Zabka Polska (about 90% of emissions) figures separately; Group intensity disclosed for the first time (no 2024 comparative)</t>
+          <t>Scope 3 category 1 partly spend-based using US EPA supply chain factors for a European supply chain; category 2 fell 82% (30,543 to 5,592 t) without explanation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mixing boundaries would distort comparison</t>
+          <t>Scope 3 (88.5% of total) driven by estimates</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Group figures used</t>
+          <t>Flagged in README</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Grupa Zabka</t>
+          <t>Grupa Kety</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2322,51 +2322,51 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Taxonomy: no eligible or aligned turnover; CapEx aligned 8.2% (eligible 58.2%, logistics centres); OpEx not material under exemption</t>
+          <t>Boundary combines operational and financial control; 2024 not recalculated for Selt acquisition (Sept 2024)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OpEx 0% means not assessed</t>
+          <t>Year-on-year trend slightly distorted</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recorded as 0%, flagged</t>
+          <t>Only 2025 used</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Grupa Kety</t>
+          <t>KGHM Polska Miedz</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Missing value</t>
+          <t>Boundary or scope difference</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Only location-based GHG intensity disclosed (242.7 t/PLN m); market-based intensity missing although ESRS E1-6 requires both</t>
+          <t>Report gives parent company (Table 125) and Group (Table 126) separately; Group used. Joint ventures are reported in Scope 3 category 15 (1,099,433 t, 43.5% of Scope 3)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Automatic MB check not possible</t>
+          <t>Large share of emissions outside Scope 1-2 boundary</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recomputed LB: 1,333,852 / 5,494.6 = 242.8, matches. Computed MB: 244.0</t>
+          <t>Group figures used; cat. 15 flagged</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grupa Kety</t>
+          <t>KGHM Polska Miedz</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2376,159 +2376,159 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scope 2 market-based (118,957 t) above location-based (112,196 t) despite 20,030 MWh of guarantees of origin; MB uses supplier-specific factors</t>
+          <t>Scope 3 category 1 fell 46.5% and category 4 fell 45.3% YoY without explanation in the report; Scope 3 total -21.5%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Same pattern as Dino</t>
+          <t>Year-on-year Scope 3 trend unreliable</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kept both values</t>
+          <t>Only 2025 used</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Grupa Kety</t>
+          <t>KGHM Polska Miedz</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Methodology unclear</t>
+          <t>Boundary or scope difference</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scope 3 category 1 partly spend-based using US EPA supply chain factors for a European supply chain; category 2 fell 82% (30,543 to 5,592 t) without explanation</t>
+          <t>Taxonomy alignment not assessed in 2025 (footnote 57), although 2024 reported aligned turnover 0.87%, CapEx 3.92%, OpEx 2.04%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Scope 3 (88.5% of total) driven by estimates</t>
+          <t>0% means not assessed; drop vs 2024 is a reporting change</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Flagged in README</t>
+          <t>Recorded as 0%, flagged</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Grupa Kety</t>
+          <t>PGE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Boundary or scope difference</t>
+          <t>Unit inconsistency</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boundary combines operational and financial control; 2024 not recalculated for Selt acquisition (Sept 2024)</t>
+          <t>Intensity published in t CO2e per PLN with 4 decimals (0.0013), i.e. 1,250-1,350 t per PLN m (+/-3.8%). Computed 1,260 (-3.1%)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Year-on-year trend slightly distorted</t>
+          <t>Validation passes only within rounding range</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Only 2025 used</t>
+          <t>Converted to t/PLN m; computed value used</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Grupa Kety</t>
+          <t>PGE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Methodology unclear</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Highest Taxonomy alignment in sample: turnover 25.5% (aluminium window and shading systems, CCM 3.5), CapEx 8.6%, OpEx 38.0%. Previous target (-25% intensity) met in 2024; new absolute Scope 1+2 target with 2024 base year, net zero by 2050</t>
+          <t>Scope 2 market-based equals location-based: market-based uses national average grid factors instead of residual mix, no contractual instruments</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Only company with material aligned turnover</t>
+          <t>Market-based not comparable with Dino or Kety (residual mix / supplier factors)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Noted in README</t>
+          <t>Flagged in README</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KGHM Polska Miedz</t>
+          <t>PGE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Boundary or scope difference</t>
+          <t>Methodology unclear</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Report gives parent company (Table 125) and Group (Table 126) separately; Group used. Joint ventures are reported in Scope 3 category 15 (1,099,433 t, 43.5% of Scope 3)</t>
+          <t>Breakdown table inconsistent: row labelled parent company (52,200,270 t) equals the Group total, while consolidated group row shows 52,199,862 t; parent + subsidiaries does not add up to consolidated</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Large share of emissions outside Scope 1-2 boundary</t>
+          <t>Internal arithmetic error in disclosure</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Group figures used; cat. 15 flagged</t>
+          <t>Group total from main E1-6 table used</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KGHM Polska Miedz</t>
+          <t>Tauron Polska Energia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Methodology unclear</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>77.9% of Scope 1 covered by EU ETS: only company in sample with regulated emissions so far</t>
+          <t>Scope 2 includes purchased electricity covering distribution grid losses (loss rate 3.5% in 2025 vs 2% in 2024), so Scope 2 LB rose 57% YoY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Carbon cost exposure, not comparable with retail</t>
+          <t>Scope 2 not comparable with non-grid companies</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Noted in README</t>
+          <t>Compare utilities only with each other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KGHM Polska Miedz</t>
+          <t>Tauron Polska Energia</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2538,341 +2538,44 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scope 2 market-based (2,105,896 t) 35% above location-based (1,554,657 t) and up 9.4% YoY; parent company S1+2 MB is +10.5% vs 2020 base year against a -30% by 2030 target</t>
+          <t>Scope 3 dominated by category 3 (11.5 Mt, 72%); category 15 investments 2.0 Mt; categories 1 and 2 spend-based, rising with spend and factors</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Moving away from target on market-based view</t>
+          <t>Scope 3 trend driven by estimates</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Flagged in README</t>
+          <t>Only 2025 used</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KGHM Polska Miedz</t>
+          <t>Tauron Polska Energia</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Methodology unclear</t>
+          <t>Boundary or scope difference</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scope 3 category 1 fell 46.5% and category 4 fell 45.3% YoY without explanation in the report; Scope 3 total -21.5%</t>
+          <t>Energy data for 2025 include TAURON Sprzedaz (PPA with guarantees of origin), not included in 2024</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Year-on-year Scope 3 trend unreliable</t>
+          <t>Energy YoY change partly boundary-driven</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>Only 2025 used</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>KGHM Polska Miedz</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Boundary or scope difference</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Taxonomy alignment not assessed in 2025 (footnote 57), although 2024 reported aligned turnover 0.87%, CapEx 3.92%, OpEx 2.04%. Table captions say 2024 but data are 2025</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>0% means not assessed; drop vs 2024 is a reporting change</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Recorded as 0%, flagged</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>PGE</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Unit inconsistency</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Intensity published in t CO2e per PLN with 4 decimals (0.0013), i.e. 1,250-1,350 t per PLN m (+/-3.8%). Computed 1,260 (-3.1%)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Validation passes only within rounding range</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Converted to t/PLN m; computed value used</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>PGE</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Methodology unclear</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Scope 2 market-based equals location-based: market-based uses national average grid factors instead of residual mix, no contractual instruments</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Market-based not comparable with Dino or Kety (residual mix / supplier factors)</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Flagged in README</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>PGE</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Methodology unclear</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Breakdown table inconsistent: row labelled parent company (52,200,270 t) equals the Group total, while consolidated group row shows 52,199,862 t; parent + subsidiaries does not add up to consolidated</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Internal arithmetic error in disclosure</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Group total from main E1-6 table used</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>PGE</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Scope 1 is 67% of total and 98.98% under EU ETS; Scope 3 dominated by category 3 (21.3 Mt, 89%), calculated only with database factors, no supplier data. Energy consumption (149.5 TWh) includes fuel burned for power generation</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Energy and emission intensities not comparable with non-utilities</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Compare utilities only with each other</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>PGE</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>High Taxonomy alignment: turnover 24.6% (grids CCM 4.9, wind CCM 4.3, rail infrastructure), CapEx 42.9%, OpEx 41.2%, while total emissions remain the highest in the sample</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Green investment coexists with coal-heavy generation</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Noted in README</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Tauron Polska Energia</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Scope 1 rose 6.3% YoY (9.24 to 9.83 Mt) due to higher coal-fired generation; 98% under EU ETS. Scope 1 is 71% of the 2022 base year; targets shown as 29% of base by 2030 and 0% by 2040</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Utility emissions driven by dispatch, not structural trend</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Noted in README</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Tauron Polska Energia</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Methodology unclear</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Scope 2 includes purchased electricity covering distribution grid losses (loss rate 3.5% in 2025 vs 2% in 2024), so Scope 2 LB rose 57% YoY</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Scope 2 not comparable with non-grid companies</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Compare utilities only with each other</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Tauron Polska Energia</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Methodology unclear</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Scope 3 dominated by category 3 (11.5 Mt, 72%); category 15 investments 2.0 Mt; categories 1 and 2 spend-based, rising with spend and factors</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Scope 3 trend driven by estimates</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Only 2025 used</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Tauron Polska Energia</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Boundary or scope difference</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Energy data for 2025 include TAURON Sprzedaz (PPA with guarantees of origin), not included in 2024</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Energy YoY change partly boundary-driven</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Only 2025 used</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Tauron Polska Energia</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Highest Taxonomy alignment in sample: turnover 38.8%, CapEx 84.5%, OpEx 74.2% (grids and renewables), despite 26.8 Mt total emissions. Intensity disclosed with 6 decimals (0.000807 t/PLN): precise, computed 806.8 matches</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Green investment coexists with coal generation (as for PGE)</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Noted in README</t>
         </is>
       </c>
     </row>
